--- a/result/mapping/mapping_done.xlsx
+++ b/result/mapping/mapping_done.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Me\thesis\Thesis code\result\mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5569F7-ACAE-472C-A4C5-A3B8A0EB1597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D83E1D-27AB-4568-8BBD-2346EBBB0D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>

--- a/result/mapping/mapping_done.xlsx
+++ b/result/mapping/mapping_done.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Me\thesis\Thesis code\result\mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8407D32F-BCD6-481C-9BC2-04E8CF7BE78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DD1D7E-69F5-4853-91F7-F8B809768F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId5"/>
+    <pivotCache cacheId="8" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -32974,7 +32974,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4A66FAA-91B2-4DA3-AC6F-F2E0BC48F171}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4A66FAA-91B2-4DA3-AC6F-F2E0BC48F171}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A667" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
